--- a/support/specifications/ccda/CCDA to FHIR Conversion Spec - General.xlsx
+++ b/support/specifications/ccda/CCDA to FHIR Conversion Spec - General.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12180" tabRatio="709" activeTab="9"/>
+    <workbookView windowWidth="28800" windowHeight="12180" tabRatio="709" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="General" sheetId="11" r:id="rId1"/>
@@ -2183,6 +2183,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">The Encounter details are taken from </t>
     </r>
     <r>
@@ -2974,7 +2981,8 @@
     <t>SHA-256 UUID generated using 
 1. Patient-MRN (the value set for 'identifier (MR) -&gt; value' of Patient Resource from Document.recordTarget.patientRole.id.extension)
 2. Value of the header variable 'X-TechBD-CIN'
-3. Content of first occurance of Document.author section</t>
+3. Content of first occurance of Document.author section
+4. Organization Name from Document.author.assignedAuthor.representedOrganization.name</t>
   </si>
   <si>
     <t>"id" : "8e4752d52cb9f94657401368f1c8e3cdb052624b10166a665e4c80cdabc62b3c",</t>
@@ -5518,13 +5526,36 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF00B050"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color rgb="FFC00000"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <i/>
       <sz val="11"/>
       <color rgb="FF00B050"/>
       <name val="Calibri"/>
@@ -5556,29 +5587,6 @@
       <color rgb="FF00B050"/>
       <name val="Segoe UI"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF00B050"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="35">
@@ -8608,7 +8616,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="4" ht="90" spans="1:6">
+    <row r="4" ht="135" spans="1:6">
       <c r="B4" t="s">
         <v>16</v>
       </c>
